--- a/DKC_S5_prix.xlsx
+++ b/DKC_S5_prix.xlsx
@@ -96087,7 +96087,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prix unitaire en euros hors taxes, par pièce (un élément rectiligne = un élément de 3 m).</t>
+          <t>Prix unitaire en euros hors taxes. Chemins de câbles (éléments rectilignes) et couvercles pour élément rectiligne : prix AU MÈTRE. Tous les autres articles : prix à la pièce.</t>
         </is>
       </c>
     </row>
